--- a/Courses/Term 3/QAM-III/903 - DATA - Jan 5 2026 - NLP - DIET FOOD.xlsx
+++ b/Courses/Term 3/QAM-III/903 - DATA - Jan 5 2026 - NLP - DIET FOOD.xlsx
@@ -1,29 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/SIRMAUR. IIM .. Nov 14 2025/T1 - Non Linear Programming/Data to students - 00 SD in Class/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9364ECF0-B8FC-6245-987E-F893048E1085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E80F5A-4952-4277-A4B4-F84BCFA1040F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" xr2:uid="{5D8423A8-FD2B-0641-B508-10861B8A6050}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5D8423A8-FD2B-0641-B508-10861B8A6050}"/>
   </bookViews>
   <sheets>
     <sheet name="Problem DIET Food" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'Problem DIET Food'!$B$14:$C$14</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">'Problem DIET Food'!$A$3</definedName>
-    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'Problem DIET Food'!$G$14</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Feedstuff</t>
   </si>
@@ -75,6 +95,24 @@
   </si>
   <si>
     <t>Diet foods problem</t>
+  </si>
+  <si>
+    <t>CORN</t>
+  </si>
+  <si>
+    <t>SOYBEAN</t>
+  </si>
+  <si>
+    <t>TOTAL FEED</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>PROTEIN</t>
+  </si>
+  <si>
+    <t>FIBER</t>
   </si>
 </sst>
 </file>
@@ -146,9 +184,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -186,7 +224,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -292,7 +330,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -434,7 +472,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -442,26 +480,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4486CBF9-AE49-7A4A-A620-8B416A5A1975}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
@@ -469,7 +507,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>0</v>
       </c>
@@ -483,7 +521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>1</v>
       </c>
@@ -497,7 +535,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -511,9 +549,53 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f>C14+B14</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>0.09*B14+0.06*C14</f>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f>0.02*C14+0.06*D14</f>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f>0.3*B14+0.9*C14</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
